--- a/exports/PHOENIXLTD_full_report.xlsx
+++ b/exports/PHOENIXLTD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.46</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>479</v>
+        <v>460.05</v>
       </c>
       <c r="I2" t="n">
         <v>475.46210790495</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>4.22</v>
+        <v>0.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.24</v>
+        <v>2.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.34</v>
       </c>
       <c r="N2" t="n">
-        <v>3.01</v>
+        <v>4.22</v>
       </c>
       <c r="O2" t="n">
         <v>-0.62</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.47</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.38541666666</v>
+        <v>44636.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>481.7</v>
+        <v>501.65</v>
       </c>
       <c r="I3" t="n">
         <v>487.9585013711728</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.71</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>10.71</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.93</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="I4" t="n">
         <v>505.0279260405786</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K4" t="n">
-        <v>2.06</v>
+        <v>-1.52</v>
       </c>
       <c r="L4" t="n">
         <v>5.25</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.73</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>539.5</v>
+        <v>552.5</v>
       </c>
       <c r="I5" t="n">
         <v>546.9896776807258</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.84</v>
       </c>
       <c r="L5" t="n">
-        <v>12.15</v>
+        <v>13.87</v>
       </c>
       <c r="M5" t="n">
         <v>0.61</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.33</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>545</v>
+        <v>509.9</v>
       </c>
       <c r="I6" t="n">
         <v>525.2975848176713</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.36</v>
+        <v>-7.71</v>
       </c>
       <c r="L6" t="n">
         <v>10.77</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>16.31</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44740.55208333334</v>
+        <v>44741.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>589</v>
+        <v>607.5</v>
       </c>
       <c r="I7" t="n">
         <v>593.0469375049936</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-15.51</v>
+        <v>-19.14</v>
       </c>
       <c r="L7" t="n">
-        <v>20.39</v>
+        <v>22.08</v>
       </c>
       <c r="M7" t="n">
         <v>1.34</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.47</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44832.38541666666</v>
+        <v>44832.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>673</v>
+        <v>664.5</v>
       </c>
       <c r="I8" t="n">
         <v>665.5506042345877</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>91</v>
+        <v>91.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>10.78</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>6.67</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44841.38541666666</v>
+        <v>44841.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>715.9</v>
+        <v>729.5</v>
       </c>
       <c r="I9" t="n">
         <v>717.9590236610918</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.74</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>10.29</v>
+        <v>10.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.27</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.52</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>712.85</v>
+        <v>704</v>
       </c>
       <c r="I10" t="n">
         <v>708.7066662032855</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>62.83333333333334</v>
+        <v>63</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.28</v>
+        <v>-3.5</v>
       </c>
       <c r="L10" t="n">
         <v>8.289999999999999</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.92</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>706</v>
+        <v>714.7</v>
       </c>
       <c r="I11" t="n">
         <v>711.0770601005178</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.28</v>
+        <v>-1.52</v>
       </c>
       <c r="L11" t="n">
         <v>3.84</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>6.9</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>695</v>
+        <v>679.5</v>
       </c>
       <c r="I12" t="n">
         <v>690.1682957409578</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.76</v>
+        <v>-4.93</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>6.88</v>
       </c>
       <c r="M12" t="n">
         <v>0.37</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.88</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>683.6</v>
+        <v>699.65</v>
       </c>
       <c r="I13" t="n">
         <v>687.6507640813651</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6</v>
+        <v>-2.97</v>
       </c>
       <c r="L13" t="n">
         <v>7.28</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44994.38541666666</v>
+        <v>44994.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>653.55</v>
+        <v>647.5</v>
       </c>
       <c r="I14" t="n">
         <v>647.9159073769293</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.59</v>
+        <v>-7.45</v>
       </c>
       <c r="L14" t="n">
-        <v>6.71</v>
+        <v>7.68</v>
       </c>
       <c r="M14" t="n">
         <v>0.11</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>7.21</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45005.55208333334</v>
+        <v>45006.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>642</v>
+        <v>660.9</v>
       </c>
       <c r="I15" t="n">
         <v>659.5606043637499</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.85</v>
+        <v>-2.07</v>
       </c>
       <c r="L15" t="n">
         <v>3.39</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3</v>
+        <v>1.23</v>
       </c>
       <c r="N15" t="n">
         <v>3.3</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.84</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45068.55208333334</v>
+        <v>45069.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>711.8</v>
+        <v>705.55</v>
       </c>
       <c r="I16" t="n">
         <v>705.6490944285093</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K16" t="n">
-        <v>7.7</v>
+        <v>6.76</v>
       </c>
       <c r="L16" t="n">
         <v>4.52</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.83</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>733</v>
+        <v>754.9</v>
       </c>
       <c r="I17" t="n">
         <v>750.4916353934682</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.89</v>
+        <v>-6.99</v>
       </c>
       <c r="L17" t="n">
-        <v>7.7</v>
+        <v>8.07</v>
       </c>
       <c r="M17" t="n">
         <v>1.97</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.58</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45203.55208333334</v>
+        <v>45204.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>905</v>
+        <v>881.5</v>
       </c>
       <c r="I18" t="n">
         <v>883.5857972960411</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>125.1666666666667</v>
+        <v>126</v>
       </c>
       <c r="K18" t="n">
-        <v>19.88</v>
+        <v>16.77</v>
       </c>
       <c r="L18" t="n">
         <v>3.35</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.33</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>928.8</v>
+        <v>961.5</v>
       </c>
       <c r="I19" t="n">
         <v>945.299531041051</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.37</v>
+        <v>-9.08</v>
       </c>
       <c r="L19" t="n">
-        <v>6.92</v>
+        <v>10.1</v>
       </c>
       <c r="M19" t="n">
         <v>2.26</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>7.84</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>925.85</v>
+        <v>913</v>
       </c>
       <c r="I20" t="n">
         <v>914.0365490398764</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.71</v>
+        <v>-5.04</v>
       </c>
       <c r="L20" t="n">
-        <v>4.52</v>
+        <v>5.15</v>
       </c>
       <c r="M20" t="n">
         <v>0.36</v>
       </c>
       <c r="N20" t="n">
-        <v>3.02</v>
+        <v>4.68</v>
       </c>
       <c r="O20" t="n">
         <v>3.49</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45231.55208333334</v>
+        <v>45232.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>942.5</v>
+        <v>976.4</v>
       </c>
       <c r="I21" t="n">
         <v>959.5680010027054</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.23</v>
+        <v>-6.94</v>
       </c>
       <c r="L21" t="n">
-        <v>4.33</v>
+        <v>7.06</v>
       </c>
       <c r="M21" t="n">
         <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>4.51</v>
       </c>
       <c r="O21" t="n">
         <v>-4.68</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.74</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45267.55208333334</v>
+        <v>45268.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1128.5</v>
+        <v>1087</v>
       </c>
       <c r="I22" t="n">
         <v>1098.34883541335</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
-        <v>15.58</v>
+        <v>11.33</v>
       </c>
       <c r="L22" t="n">
         <v>4.21</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45295.38541666666</v>
+        <v>45295.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1175</v>
+        <v>1190.05</v>
       </c>
       <c r="I23" t="n">
         <v>1182.518743758254</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.1</v>
+        <v>-9.48</v>
       </c>
       <c r="L23" t="n">
         <v>10.98</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.17</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>1223.4</v>
+        <v>1181</v>
       </c>
       <c r="I24" t="n">
         <v>1185.893246026909</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>-0.76</v>
       </c>
       <c r="L24" t="n">
         <v>2.16</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.79</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1234</v>
+        <v>1292.3</v>
       </c>
       <c r="I25" t="n">
         <v>1274.794291177748</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.49</v>
+        <v>-9.42</v>
       </c>
       <c r="L25" t="n">
-        <v>6.27</v>
+        <v>13.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.31</v>
       </c>
       <c r="N25" t="n">
-        <v>5.51</v>
+        <v>7.78</v>
       </c>
       <c r="O25" t="n">
         <v>-5.44</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>11.87</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1435</v>
+        <v>1294.4</v>
       </c>
       <c r="I26" t="n">
         <v>1318.798333484406</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K26" t="n">
-        <v>11.04</v>
+        <v>0.16</v>
       </c>
       <c r="L26" t="n">
         <v>5.48</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="N26" t="n">
-        <v>5.26</v>
+        <v>7.67</v>
       </c>
       <c r="O26" t="n">
         <v>7.78</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>22.59</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1415</v>
+        <v>1450.25</v>
       </c>
       <c r="I27" t="n">
         <v>1424.28284181732</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.32</v>
+        <v>-12.04</v>
       </c>
       <c r="L27" t="n">
         <v>14.79</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1473.15</v>
+        <v>1417</v>
       </c>
       <c r="I28" t="n">
         <v>1463.011708680326</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K28" t="n">
-        <v>1.58</v>
+        <v>-2.29</v>
       </c>
       <c r="L28" t="n">
         <v>3.48</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>12.09</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1502.5</v>
+        <v>1565</v>
       </c>
       <c r="I29" t="n">
         <v>1550.741078417527</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.03</v>
+        <v>-10.44</v>
       </c>
       <c r="L29" t="n">
-        <v>8.359999999999999</v>
+        <v>12.64</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7</v>
+        <v>3.83</v>
       </c>
       <c r="N29" t="n">
         <v>4.73</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45492.55208333334</v>
+        <v>45495.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1975</v>
+        <v>1811.15</v>
       </c>
       <c r="I30" t="n">
         <v>1884.957569455231</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>65</v>
       </c>
       <c r="K30" t="n">
-        <v>26.2</v>
+        <v>15.73</v>
       </c>
       <c r="L30" t="n">
         <v>6.36</v>
@@ -2151,7 +2510,7 @@
         <v>2.53</v>
       </c>
       <c r="N30" t="n">
-        <v>4.76</v>
+        <v>5.87</v>
       </c>
       <c r="O30" t="n">
         <v>4.16</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1754.5</v>
+        <v>1829.8</v>
       </c>
       <c r="I31" t="n">
         <v>1799.718431670524</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>3.13</v>
+        <v>-1.03</v>
       </c>
       <c r="L31" t="n">
         <v>9.050000000000001</v>
@@ -2208,7 +2579,7 @@
         <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>3.28</v>
+        <v>5.04</v>
       </c>
       <c r="O31" t="n">
         <v>-5.87</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45546.38541666666</v>
+        <v>45546.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1748.6</v>
+        <v>1720</v>
       </c>
       <c r="I32" t="n">
         <v>1721.735089386999</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.44</v>
+        <v>-6</v>
       </c>
       <c r="L32" t="n">
-        <v>5.38</v>
+        <v>6.27</v>
       </c>
       <c r="M32" t="n">
         <v>0.59</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1734</v>
+        <v>1940</v>
       </c>
       <c r="I33" t="n">
         <v>1809.006633265955</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-12.79</v>
       </c>
       <c r="L33" t="n">
-        <v>9.300000000000001</v>
+        <v>13.37</v>
       </c>
       <c r="M33" t="n">
         <v>4.18</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>17.65</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45579.38541666666</v>
+        <v>45579.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1630.55</v>
+        <v>1608.8</v>
       </c>
       <c r="I34" t="n">
         <v>1615.53869522843</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K34" t="n">
-        <v>-15.95</v>
+        <v>-17.07</v>
       </c>
       <c r="L34" t="n">
         <v>19.59</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.49</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1520</v>
+        <v>1588.6</v>
       </c>
       <c r="I35" t="n">
         <v>1587.982922680551</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>5.52</v>
+        <v>1.26</v>
       </c>
       <c r="L35" t="n">
         <v>4.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.71</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1769</v>
+        <v>1726.9</v>
       </c>
       <c r="I36" t="n">
         <v>1732.07591949024</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K36" t="n">
-        <v>11.36</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>12.37</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.55</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45665.55208333334</v>
+        <v>45666.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1650</v>
+        <v>1682.05</v>
       </c>
       <c r="I37" t="n">
         <v>1680.358553788997</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>4.45</v>
+        <v>2.6</v>
       </c>
       <c r="L37" t="n">
         <v>4.11</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>11.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1531</v>
+        <v>1459.05</v>
       </c>
       <c r="I38" t="n">
         <v>1495.803109823135</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.98</v>
+        <v>-13.26</v>
       </c>
       <c r="L38" t="n">
-        <v>10.73</v>
+        <v>13.72</v>
       </c>
       <c r="M38" t="n">
         <v>0.8</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>13.6</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1587</v>
+        <v>1633.1</v>
       </c>
       <c r="I39" t="n">
         <v>1613.533964116369</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.77</v>
+        <v>-11.93</v>
       </c>
       <c r="L39" t="n">
-        <v>11.58</v>
+        <v>13.02</v>
       </c>
       <c r="M39" t="n">
         <v>0.47</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>10.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1696.9</v>
+        <v>1640.45</v>
       </c>
       <c r="I40" t="n">
         <v>1648.572313424226</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>3.91</v>
+        <v>0.45</v>
       </c>
       <c r="L40" t="n">
         <v>3.8</v>
       </c>
       <c r="M40" t="n">
-        <v>0.45</v>
+        <v>1.59</v>
       </c>
       <c r="N40" t="n">
-        <v>4.47</v>
+        <v>4.65</v>
       </c>
       <c r="O40" t="n">
         <v>3.3</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.2</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45727.38541666666</v>
+        <v>45727.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>1616.2</v>
+        <v>1659.5</v>
       </c>
       <c r="I41" t="n">
         <v>1619.536383496193</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>1.48</v>
+        <v>-1.16</v>
       </c>
       <c r="L41" t="n">
         <v>3.33</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1578</v>
+        <v>1555.7</v>
       </c>
       <c r="I42" t="n">
         <v>1561.951128147197</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.91</v>
+        <v>-6.25</v>
       </c>
       <c r="L42" t="n">
-        <v>8.15</v>
+        <v>10.81</v>
       </c>
       <c r="M42" t="n">
-        <v>0.91</v>
+        <v>4.85</v>
       </c>
       <c r="N42" t="n">
         <v>3.57</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.06</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45764.38541666666</v>
+        <v>45764.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1607</v>
+        <v>1615</v>
       </c>
       <c r="I43" t="n">
         <v>1611.673261838388</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.3</v>
+        <v>-3.81</v>
       </c>
       <c r="L43" t="n">
         <v>4.78</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1653</v>
+        <v>1531.7</v>
       </c>
       <c r="I44" t="n">
         <v>1567.777989623954</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>2.35</v>
+        <v>-5.16</v>
       </c>
       <c r="L44" t="n">
-        <v>1.24</v>
+        <v>5.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0.19</v>
+        <v>2.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.47</v>
+        <v>7.25</v>
       </c>
       <c r="O44" t="n">
         <v>1.19</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.83</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45793.55208333334</v>
+        <v>45796.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1550</v>
+        <v>1606</v>
       </c>
       <c r="I45" t="n">
         <v>1594.861287213375</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.19</v>
+        <v>-4.85</v>
       </c>
       <c r="L45" t="n">
         <v>7.33</v>
@@ -3006,7 +3545,7 @@
         <v>2.02</v>
       </c>
       <c r="N45" t="n">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="O45" t="n">
         <v>-7.25</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1562</v>
+        <v>1545.5</v>
       </c>
       <c r="I46" t="n">
         <v>1554.846869486885</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.74</v>
+        <v>-3.77</v>
       </c>
       <c r="L46" t="n">
         <v>5</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.25</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1448.9</v>
+        <v>1540.5</v>
       </c>
       <c r="I47" t="n">
         <v>1509.075364514826</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>6.25</v>
+        <v>0.32</v>
       </c>
       <c r="L47" t="n">
         <v>2.23</v>
@@ -3120,7 +3683,7 @@
         <v>1.15</v>
       </c>
       <c r="N47" t="n">
-        <v>1.72</v>
+        <v>4.84</v>
       </c>
       <c r="O47" t="n">
         <v>-1.02</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.49</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1470.2</v>
+        <v>1440.4</v>
       </c>
       <c r="I48" t="n">
         <v>1441.201954742991</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.56</v>
+        <v>-6.5</v>
       </c>
       <c r="L48" t="n">
-        <v>6.46</v>
+        <v>6.95</v>
       </c>
       <c r="M48" t="n">
         <v>1.2</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>6.6</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1489.6</v>
+        <v>1506.4</v>
       </c>
       <c r="I49" t="n">
         <v>1501.756378981551</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.42</v>
+        <v>-4.58</v>
       </c>
       <c r="L49" t="n">
-        <v>3.98</v>
+        <v>4.76</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.65</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1517.4</v>
+        <v>1507.2</v>
       </c>
       <c r="I50" t="n">
         <v>1509.699476850829</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>0.73</v>
+        <v>0.05</v>
       </c>
       <c r="L50" t="n">
         <v>2.36</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.62</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1559</v>
+        <v>1590.1</v>
       </c>
       <c r="I51" t="n">
         <v>1577.396390914354</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.44</v>
+        <v>-5.5</v>
       </c>
       <c r="L51" t="n">
         <v>5.99</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1573.3</v>
+        <v>1556.3</v>
       </c>
       <c r="I52" t="n">
         <v>1573.259261458866</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.06</v>
+        <v>-2.13</v>
       </c>
       <c r="L52" t="n">
         <v>2.3</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.22</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45943.55208333334</v>
+        <v>45944.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1624</v>
+        <v>1639.1</v>
       </c>
       <c r="I53" t="n">
         <v>1625.078231068127</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.35</v>
+        <v>-5.32</v>
       </c>
       <c r="L53" t="n">
-        <v>4.59</v>
+        <v>6.96</v>
       </c>
       <c r="M53" t="n">
         <v>1.14</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.97</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1713.3</v>
+        <v>1672</v>
       </c>
       <c r="I54" t="n">
         <v>1678.219363964971</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>4.53</v>
+        <v>2.01</v>
       </c>
       <c r="L54" t="n">
         <v>1.44</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.14</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1770.4</v>
+        <v>1775.7</v>
       </c>
       <c r="I55" t="n">
         <v>1774.580868541568</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.89</v>
+        <v>-6.2</v>
       </c>
       <c r="L55" t="n">
-        <v>6.22</v>
+        <v>6.54</v>
       </c>
       <c r="M55" t="n">
         <v>1.08</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.85</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1910</v>
+        <v>1871</v>
       </c>
       <c r="I56" t="n">
         <v>1872.735824884183</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K56" t="n">
-        <v>7.56</v>
+        <v>5.37</v>
       </c>
       <c r="L56" t="n">
         <v>1.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.08</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1735.4</v>
+        <v>1749.3</v>
       </c>
       <c r="I57" t="n">
         <v>1745.436435044574</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K57" t="n">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="L57" t="n">
         <v>6.52</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46079.55208333334</v>
+        <v>46080.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1706.3</v>
+        <v>1672.8</v>
       </c>
       <c r="I58" t="n">
         <v>1678.764787722359</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.46</v>
+        <v>-4.37</v>
       </c>
       <c r="L58" t="n">
         <v>4.7</v>
@@ -3747,7 +4442,7 @@
         <v>0.79</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="O58" t="n">
         <v>0.84</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.8</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.38541666666</v>
+        <v>46119.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1583.2</v>
+        <v>1600</v>
       </c>
       <c r="I59" t="n">
         <v>1592.726190073353</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>5.36</v>
+        <v>4.35</v>
       </c>
       <c r="L59" t="n">
         <v>2.27</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.95</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1755.2</v>
+        <v>1732</v>
       </c>
       <c r="I60" t="n">
         <v>1733.201871611014</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K60" t="n">
-        <v>9.699999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="L60" t="n">
         <v>1.38</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.22</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1750.1</v>
+        <v>1807.5</v>
       </c>
       <c r="I61" t="n">
         <v>1794.157290355385</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.05</v>
+        <v>-4.36</v>
       </c>
       <c r="L61" t="n">
         <v>5.04</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.24</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2040</v>
+        <v>1903.6</v>
       </c>
       <c r="I62" t="n">
         <v>2013.409169518034</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K62" t="n">
-        <v>12.86</v>
+        <v>5.32</v>
       </c>
       <c r="L62" t="n">
         <v>4.75</v>
       </c>
       <c r="M62" t="n">
-        <v>1.34</v>
+        <v>2.46</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>6.72</v>
       </c>
       <c r="O62" t="n">
         <v>0.79</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.23</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1900</v>
+        <v>1940.8</v>
       </c>
       <c r="I63" t="n">
         <v>1937.999700805847</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>0.19</v>
+        <v>-1.95</v>
       </c>
       <c r="L63" t="n">
         <v>4.9</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.67</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1929.2</v>
+        <v>1861.3</v>
       </c>
       <c r="I64" t="n">
         <v>1900.674855407311</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.6</v>
+        <v>-4.1</v>
       </c>
       <c r="L64" t="n">
-        <v>2.11</v>
+        <v>4.28</v>
       </c>
       <c r="M64" t="n">
         <v>1.44</v>
       </c>
       <c r="N64" t="n">
-        <v>1.81</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
         <v>1.63</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1887</v>
+        <v>1899.4</v>
       </c>
       <c r="I65" t="n">
         <v>1897.377254269009</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.38</v>
+        <v>-2.05</v>
       </c>
       <c r="L65" t="n">
         <v>4.59</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>18</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7105,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.1</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7115,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7125,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125.2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7135,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="11">
@@ -6398,7 +7195,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.23</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.89</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.42</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7225,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.2</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7235,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.2</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.02</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.39</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -6488,7 +7285,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -6498,7 +7295,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.03</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="27">
@@ -6538,7 +7335,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
